--- a/tests/DotnetPoi.Interop.Tests/fixtures/from-dotnet-poi/phase5-step1-formulas.xlsx
+++ b/tests/DotnetPoi.Interop.Tests/fixtures/from-dotnet-poi/phase5-step1-formulas.xlsx
@@ -1,13 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908" codeName="{51196F13-6AD0-C1B8-E2B4-A1F9AE17003E}"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurajwilkinson/Documents/Crossref/(local) Education files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10001_{3DCA316C-72F0-934C-8F60-896D65101522}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="7040" yWindow="900" windowWidth="21040" windowHeight="15540" xr2:uid="{F78FA456-F914-C943-93AA-62638AC4422C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Formulas" r:id="rId3" sheetId="1"/>
+    <sheet name="Formulas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="doicreator">Data_sheet!$G$3</definedName>
+    <definedName name="noofdois">Form!$B$5</definedName>
+    <definedName name="prefix">Form!$B$4</definedName>
+    <definedName name="RANDOMF">Data_sheet!$G$2</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/tests/DotnetPoi.Interop.Tests/fixtures/from-dotnet-poi/phase5-step1-formulas.xlsx
+++ b/tests/DotnetPoi.Interop.Tests/fixtures/from-dotnet-poi/phase5-step1-formulas.xlsx
@@ -1,38 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908" codeName="{51196F13-6AD0-C1B8-E2B4-A1F9AE17003E}"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurajwilkinson/Documents/Crossref/(local) Education files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10001_{3DCA316C-72F0-934C-8F60-896D65101522}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="7040" yWindow="900" windowWidth="21040" windowHeight="15540" xr2:uid="{F78FA456-F914-C943-93AA-62638AC4422C}"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Formulas" sheetId="1" r:id="rId1"/>
+    <sheet name="Formulas" r:id="rId3" sheetId="1"/>
   </sheets>
-  <definedNames>
-    <definedName name="doicreator">Data_sheet!$G$3</definedName>
-    <definedName name="noofdois">Form!$B$5</definedName>
-    <definedName name="prefix">Form!$B$4</definedName>
-    <definedName name="RANDOMF">Data_sheet!$G$2</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 

--- a/tests/DotnetPoi.Interop.Tests/fixtures/from-dotnet-poi/phase5-step1-formulas.xlsx
+++ b/tests/DotnetPoi.Interop.Tests/fixtures/from-dotnet-poi/phase5-step1-formulas.xlsx
@@ -78,6 +78,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins bottom="0.7500" footer="0.3000" header="0.3000" left="0.7000" right="0.7000" top="0.7500"/>
 </worksheet>
 </file>